--- a/public/Gararge and Gate RK data.xlsx
+++ b/public/Gararge and Gate RK data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tapsy\All Remotes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\allremotes\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21C998B-288C-47B9-9FC7-F7144F7E2FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59EAD54-B55D-4150-BDA1-71141A33F57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5F8A3AC-6C46-4C8B-AB8F-6DEFFE490B42}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5F8A3AC-6C46-4C8B-AB8F-6DEFFE490B42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9129,7 +9129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="165" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="150" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>535</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="165" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>536</v>
       </c>
@@ -9211,7 +9211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="225" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="210" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>537</v>
       </c>
@@ -9278,7 +9278,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="195" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="180" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -9418,7 +9418,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="225" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="210" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>541</v>
       </c>
@@ -9970,7 +9970,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="225" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="210" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>556</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="315" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="300" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>560</v>
       </c>
@@ -10145,7 +10145,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="315" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="285" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>561</v>
       </c>
@@ -12029,7 +12029,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>609</v>
       </c>
@@ -16938,7 +16938,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="215" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>733</v>
       </c>
@@ -17128,7 +17128,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="220" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>738</v>
       </c>
